--- a/国库列表模板.xlsx
+++ b/国库列表模板.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,20 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="002E5F8A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +63,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,17 +102,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,11 +492,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -474,6 +513,21 @@
           <t>国库名称</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>下载全辖</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>下载本级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -481,21 +535,51 @@
           <t>101001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>XX市国库</t>
         </is>
       </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>市级国库，全辖+本级均下载</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>101002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>XX区国库1</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>区级国库，仅下载本级</t>
         </is>
       </c>
     </row>
@@ -505,23 +589,49 @@
           <t>101003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>XX区国库2</t>
         </is>
       </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>区级国库，仅下载本级</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>101004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>XX县国库1</t>
         </is>
       </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -529,23 +639,45 @@
           <t>101005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>XX县国库2</t>
         </is>
       </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>101006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>XX县国库3</t>
         </is>
       </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -553,23 +685,45 @@
           <t>101007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>XX县国库4</t>
         </is>
       </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>101008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>XX县国库5</t>
         </is>
       </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -577,23 +731,45 @@
           <t>101009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>XX县国库6</t>
         </is>
       </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>101010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>XX县国库7</t>
         </is>
       </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -601,23 +777,45 @@
           <t>101011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>XX县国库8</t>
         </is>
       </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>101012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>XX县国库9</t>
         </is>
       </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -625,25 +823,80 @@
           <t>101013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>XX县国库10</t>
         </is>
       </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>101014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>XX县国库11</t>
         </is>
       </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>说明：</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>· 下载全辖 / 下载本级：填「是」或「否」，两列均可独立配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>· 国库代码须与系统完全一致（数字字符串，不含空格）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>· 年报由程序界面统一控制（2024~2025年），无需在此配置</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>